--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104690_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104690_W26.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3877</v>
+        <v>5.9435</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8791</v>
+        <v>3.7596</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5086</v>
+        <v>2.1839</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4052</v>
+        <v>3.2098</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8645</v>
+        <v>2.5049</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5407</v>
+        <v>0.7049</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3033</v>
+        <v>2.9646</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9599</v>
+        <v>2.7784</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3434</v>
+        <v>0.1862</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1019</v>
+        <v>0.2452</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0954</v>
+        <v>-0.2734</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1973</v>
+        <v>0.5187</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1017</v>
+        <v>1.0115</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8026</v>
+        <v>0.2111</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2991</v>
+        <v>0.8005</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.7071</v>
+        <v>1.9497</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.9497</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2214</v>
+        <v>5.7722</v>
       </c>
       <c r="E3" t="n">
-        <v>2.562</v>
+        <v>2.2884</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6594</v>
+        <v>3.4838</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7941</v>
+        <v>3.7899</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3765</v>
+        <v>1.3785</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4176</v>
+        <v>2.4114</v>
       </c>
       <c r="J3" t="n">
-        <v>3.233</v>
+        <v>3.1996</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8977</v>
+        <v>1.8821</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3353</v>
+        <v>1.3175</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5611</v>
+        <v>0.5903</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0823</v>
+        <v>1.0939</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2251</v>
+        <v>1.7758</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5293</v>
+        <v>0.2968</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6958</v>
+        <v>1.479</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6792</v>
+        <v>5.5563</v>
       </c>
       <c r="E4" t="n">
-        <v>3.675</v>
+        <v>3.6768</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0042</v>
+        <v>1.8795</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2122</v>
+        <v>3.3938</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5138</v>
+        <v>1.8504</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6984</v>
+        <v>1.5434</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9848</v>
+        <v>3.2776</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7982</v>
+        <v>1.937</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1866</v>
+        <v>1.3405</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2274</v>
+        <v>0.1162</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2844</v>
+        <v>-0.0866</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5118</v>
+        <v>0.2028</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7334000000000001</v>
+        <v>1.2716</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0907</v>
+        <v>0.6268</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6427</v>
+        <v>0.6448</v>
       </c>
       <c r="V4" t="n">
-        <v>1.9604</v>
+        <v>-0.7025</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9604</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2545</v>
+        <v>4.2292</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2575</v>
+        <v>1.483</v>
       </c>
       <c r="F5" t="n">
-        <v>2.997</v>
+        <v>2.7462</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8443</v>
+        <v>2.8355</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1486</v>
+        <v>-1.1488</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9929</v>
+        <v>3.9843</v>
       </c>
       <c r="J5" t="n">
-        <v>2.806</v>
+        <v>2.7771</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3605</v>
+        <v>-0.3727</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1665</v>
+        <v>3.1498</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0383</v>
+        <v>0.0584</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>1.276</v>
+        <v>1.2555</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1875</v>
+        <v>0.0717</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4635</v>
+        <v>1.1839</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.0478</v>
+        <v>3.907</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5542</v>
+        <v>2.0399</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4936</v>
+        <v>1.8671</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7883</v>
+        <v>1.8058</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8746</v>
+        <v>-0.8623</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6629</v>
+        <v>2.6681</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6853</v>
+        <v>2.6789</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2598</v>
+        <v>0.2586</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4256</v>
+        <v>2.4204</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8971</v>
+        <v>-0.8731</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1254</v>
+        <v>0.963</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9043</v>
+        <v>-0.4114</v>
       </c>
       <c r="U6" t="n">
-        <v>2.0297</v>
+        <v>1.3744</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7125</v>
+        <v>3.2964</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.38</v>
+        <v>0.0815</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0925</v>
+        <v>3.215</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8025</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2064</v>
+        <v>0.204</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6077</v>
+        <v>0.5984</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5889</v>
+        <v>1.5613</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9626</v>
+        <v>0.9513</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6263</v>
+        <v>0.61</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7749</v>
+        <v>-0.7588</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.007</v>
+        <v>0.5819</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8347</v>
+        <v>-0.3417</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8278</v>
+        <v>0.9236</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1021</v>
+        <v>2.5386</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5858</v>
+        <v>1.9354</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5163</v>
+        <v>0.6032</v>
       </c>
       <c r="G8" t="n">
-        <v>0.759</v>
+        <v>0.7591</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0852</v>
+        <v>-0.0771</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4107</v>
+        <v>2.393</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2614</v>
+        <v>2.244</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6516</v>
+        <v>-1.6339</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4171</v>
+        <v>-1.4078</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0236</v>
+        <v>0.4623</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5565</v>
+        <v>-0.1813</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.6437</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3287</v>
+        <v>0.4659</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1297</v>
+        <v>-0.9368</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4584</v>
+        <v>1.4027</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2919</v>
+        <v>-0.8326</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2972</v>
+        <v>0.7813</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0053</v>
+        <v>-1.6139</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.921</v>
+        <v>-0.8923</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.769</v>
+        <v>0.71</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.152</v>
+        <v>-1.6023</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6291</v>
+        <v>0.0597</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4718</v>
+        <v>0.0713</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1573</v>
+        <v>-0.0116</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1669</v>
+        <v>0.388</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2087</v>
+        <v>-0.2023</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3756</v>
+        <v>0.5903</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.002</v>
+        <v>0.2625</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2564</v>
+        <v>-1.1381</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2544</v>
+        <v>1.4006</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8173</v>
+        <v>-0.2973</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7821</v>
+        <v>-0.2986</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5994</v>
+        <v>0.0013</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8606</v>
+        <v>-0.929</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7202</v>
+        <v>-0.7724</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5808</v>
+        <v>-0.1566</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0433</v>
+        <v>0.6317</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0619</v>
+        <v>0.4738</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0186</v>
+        <v>0.1579</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0919</v>
+        <v>0.1046</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5565</v>
+        <v>-0.2091</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4645</v>
+        <v>0.3137</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3317</v>
+        <v>-0.4755</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4421</v>
+        <v>-1.7009</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1104</v>
+        <v>1.2255</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1274</v>
+        <v>1.1282</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6262</v>
+        <v>0.6261</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5011</v>
+        <v>0.502</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9109</v>
+        <v>0.8961</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3912</v>
+        <v>0.3825</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2165</v>
+        <v>0.232</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9699</v>
+        <v>0.8305</v>
       </c>
       <c r="T11" t="n">
-        <v>0.369</v>
+        <v>0.1345</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6009</v>
+        <v>0.6959</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6253</v>
+        <v>-0.5903</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1376</v>
+        <v>-0.1387</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4877</v>
+        <v>-0.4516</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6461</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4676</v>
+        <v>-0.4654</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1786</v>
+        <v>-0.1772</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0893</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.7315</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5254</v>
+        <v>-1.9599</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.13</v>
+        <v>-2.9031</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6046</v>
+        <v>0.9432</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6786</v>
+        <v>-0.6821</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0172</v>
+        <v>-1.0249</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3386</v>
+        <v>0.3428</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0558</v>
+        <v>1.0387</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3841</v>
+        <v>0.3685</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7344</v>
+        <v>-1.7209</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4012</v>
+        <v>-1.3934</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3478</v>
+        <v>0.223</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5565</v>
+        <v>-0.2998</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2087</v>
+        <v>0.5228</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9961</v>
+        <v>1.0032</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.9961</v>
+        <v>1.0032</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>28.2495</v>
+        <v>28.9459</v>
       </c>
       <c r="E14" t="n">
-        <v>8.037800000000001</v>
+        <v>8.446999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>20.2117</v>
+        <v>20.4991</v>
       </c>
       <c r="G14" t="n">
-        <v>15.3106</v>
+        <v>15.27</v>
       </c>
       <c r="H14" t="n">
-        <v>4.408599999999999</v>
+        <v>4.3814</v>
       </c>
       <c r="I14" t="n">
-        <v>10.902</v>
+        <v>10.8884</v>
       </c>
       <c r="J14" t="n">
-        <v>19.2864</v>
+        <v>19.0545</v>
       </c>
       <c r="K14" t="n">
-        <v>10.5576</v>
+        <v>10.419</v>
       </c>
       <c r="L14" t="n">
-        <v>8.728900000000001</v>
+        <v>8.6355</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.9758</v>
+        <v>-3.7847</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.148700000000001</v>
+        <v>-6.037300000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>2.1731</v>
+        <v>2.2528</v>
       </c>
       <c r="P14" t="n">
-        <v>2.268400000000001</v>
+        <v>2.2765</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.6099</v>
+        <v>-13.6579</v>
       </c>
       <c r="R14" t="n">
-        <v>15.8784</v>
+        <v>15.9343</v>
       </c>
       <c r="S14" t="n">
-        <v>8.196200000000001</v>
+        <v>8.920000000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0131</v>
+        <v>-0.3047000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>9.209299999999999</v>
+        <v>9.2249</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4743</v>
+        <v>2.4796</v>
       </c>
       <c r="W14" t="n">
-        <v>3.3745</v>
+        <v>3.3548</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.9002000000000001</v>
+        <v>-0.8751999999999993</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9623</v>
+        <v>4.0192</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3829</v>
+        <v>4.4723</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4206</v>
+        <v>-0.4531</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8649</v>
+        <v>2.8659</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2438</v>
+        <v>2.2431</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6211</v>
+        <v>0.6227</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6497</v>
+        <v>4.6272</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0477</v>
+        <v>3.0337</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7848</v>
+        <v>-1.7613</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8099</v>
+        <v>-0.7572</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9739</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1639</v>
+        <v>0.1002</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SYLLA</t>
+          <t>S. LAZAREVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0034</v>
+        <v>-0.1463</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2434</v>
+        <v>0.0911</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.24</v>
+        <v>-0.2375</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9515</v>
+        <v>-0.5089</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0288</v>
+        <v>0.6634</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07729999999999999</v>
+        <v>-1.1723</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1256</v>
+        <v>0.967</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.163</v>
+        <v>1.9133</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0373</v>
+        <v>-0.9463</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8258</v>
+        <v>-1.4759</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8658</v>
+        <v>-1.2499</v>
       </c>
       <c r="O16" t="n">
-        <v>0.04</v>
+        <v>-0.226</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2743</v>
+        <v>-0.3902</v>
       </c>
       <c r="T16" t="n">
-        <v>0.369</v>
+        <v>-0.6483</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.2581</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. LAZAREVIC</t>
+          <t>A. SYLLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0827</v>
+        <v>-0.3694</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.2342</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0745</v>
+        <v>-0.1351</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5105</v>
+        <v>-0.9488</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6623</v>
+        <v>-1.031</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1728</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9838</v>
+        <v>-0.1319</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9222</v>
+        <v>-0.1691</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.9383</v>
+        <v>0.0372</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4944</v>
+        <v>-0.8169</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2599</v>
+        <v>-0.8618</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2345</v>
+        <v>0.0449</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3188</v>
+        <v>-0.1035</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7652</v>
+        <v>-0.1024</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4464</v>
+        <v>-0.0011</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9939</v>
+        <v>-0.965</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2941</v>
+        <v>-0.3068</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6999</v>
+        <v>-0.6582</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1207</v>
+        <v>-1.1241</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0966</v>
+        <v>-1.0971</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.024</v>
+        <v>-0.0269</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1929</v>
+        <v>0.1811</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2149</v>
+        <v>-0.2208</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3135</v>
+        <v>-1.3052</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8817</v>
+        <v>-0.8763</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3269</v>
+        <v>-0.2962</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4869</v>
+        <v>-0.4879</v>
       </c>
       <c r="U18" t="n">
-        <v>0.16</v>
+        <v>0.1917</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0292</v>
+        <v>-1.899</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3927</v>
+        <v>-1.2793</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6365</v>
+        <v>-0.6197</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4133</v>
+        <v>-1.403</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4907</v>
+        <v>-1.4852</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.7007</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.7023</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O19" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9769</v>
+        <v>-0.8618</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6956</v>
+        <v>-0.5786</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2813</v>
+        <v>-0.2832</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1164</v>
+        <v>-2.8403</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9028</v>
+        <v>-1.9347</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2136</v>
+        <v>-0.9056</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1549</v>
+        <v>-2.1585</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4863</v>
+        <v>-0.4854</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6687</v>
+        <v>-1.673</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4321</v>
+        <v>0.407</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1763</v>
+        <v>0.1616</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.587</v>
+        <v>-2.5654</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.9245</v>
+        <v>-1.9184</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9615</v>
+        <v>-0.6818</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9739</v>
+        <v>-0.9758</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0124</v>
+        <v>0.294</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3841</v>
+        <v>-3.2939</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6858</v>
+        <v>-2.7126</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6984</v>
+        <v>-0.5813</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5282</v>
+        <v>0.5311</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2021</v>
+        <v>-0.1957</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7268</v>
       </c>
       <c r="J21" t="n">
-        <v>1.119</v>
+        <v>1.1044</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2185</v>
+        <v>0.2081</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5908</v>
+        <v>-0.5733</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1411</v>
+        <v>-1.051</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7652</v>
+        <v>-0.7667</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3759</v>
+        <v>-0.2843</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. PANTZAR</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9422</v>
+        <v>-4.0552</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8975</v>
+        <v>-3.489</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0447</v>
+        <v>-0.5662</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.599</v>
+        <v>-3.1063</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2135</v>
+        <v>-1.1726</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8125</v>
+        <v>-1.9337</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6675</v>
+        <v>-1.0567</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2224</v>
+        <v>0.1207</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4451</v>
+        <v>-1.1773</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.2665</v>
+        <v>-2.0496</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0089</v>
+        <v>-1.2932</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.2576</v>
+        <v>-0.7563</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.277</v>
+        <v>-0.9489</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3912</v>
+        <v>-1.0665</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1142</v>
+        <v>0.1176</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>M. PANTZAR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2113</v>
+        <v>-4.1393</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5873</v>
+        <v>-1.6966</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6241</v>
+        <v>-2.4428</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1162</v>
+        <v>-1.5886</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1863</v>
+        <v>0.218</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9299</v>
+        <v>-1.8066</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0437</v>
+        <v>1.649</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1212</v>
+        <v>1.2098</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1649</v>
+        <v>0.4392</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0725</v>
+        <v>-3.2376</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3075</v>
+        <v>-0.9918</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7649</v>
+        <v>-2.2458</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0951</v>
+        <v>-0.4809</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1825</v>
+        <v>-1.1572</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.6763</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.9317</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="24">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2761</v>
+        <v>-4.2603</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4661</v>
+        <v>-4.3758</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1901</v>
+        <v>0.1154</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.6075</v>
+        <v>-3.61</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.619</v>
+        <v>-1.6198</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.9885</v>
+        <v>-1.9902</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.974</v>
+        <v>-2.9947</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6896</v>
+        <v>-0.7002</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6335</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2149</v>
+        <v>-1.1951</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9043</v>
+        <v>-0.7877</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3106</v>
+        <v>-0.4074</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7752</v>
+        <v>-4.92</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1576</v>
+        <v>-4.5507</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6176</v>
+        <v>-0.3693</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.2057</v>
+        <v>-2.2032</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0707</v>
+        <v>-0.0717</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.1351</v>
+        <v>-2.1315</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5196</v>
+        <v>-0.5433</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4187</v>
+        <v>0.403</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.9383</v>
+        <v>-0.9463</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.6861</v>
+        <v>-1.6599</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6887</v>
+        <v>-0.8258</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3962</v>
+        <v>-0.7506</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2925</v>
+        <v>-0.0752</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,64 +2437,64 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.404</v>
+        <v>-5.3793</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.6067</v>
+        <v>-4.6407</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7973</v>
+        <v>-0.7386</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.0243</v>
+        <v>-2.0155</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3478</v>
+        <v>-0.3475</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.6765</v>
+        <v>-1.668</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2909</v>
+        <v>0.2761</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1416</v>
+        <v>0.1272</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.3152</v>
+        <v>-2.2916</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6596</v>
+        <v>-0.6306</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.0434</v>
+        <v>-1.0455</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3838</v>
+        <v>0.4149</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-28.2494</v>
+        <v>-28.2488</v>
       </c>
       <c r="E27" t="n">
-        <v>-20.3725</v>
+        <v>-20.657</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.8771</v>
+        <v>-7.592</v>
       </c>
       <c r="G27" t="n">
-        <v>-15.3105</v>
+        <v>-15.2699</v>
       </c>
       <c r="H27" t="n">
-        <v>-4.408700000000001</v>
+        <v>-4.3815</v>
       </c>
       <c r="I27" t="n">
-        <v>-10.902</v>
+        <v>-10.8885</v>
       </c>
       <c r="J27" t="n">
-        <v>3.9759</v>
+        <v>3.7845</v>
       </c>
       <c r="K27" t="n">
-        <v>6.148700000000001</v>
+        <v>6.037599999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.1729</v>
+        <v>-2.253100000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-19.2863</v>
+        <v>-19.0544</v>
       </c>
       <c r="N27" t="n">
-        <v>-10.5574</v>
+        <v>-10.4189</v>
       </c>
       <c r="O27" t="n">
-        <v>-8.728899999999999</v>
+        <v>-8.6355</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.2684</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q27" t="n">
-        <v>-15.8783</v>
+        <v>-15.9342</v>
       </c>
       <c r="R27" t="n">
-        <v>13.6101</v>
+        <v>13.6581</v>
       </c>
       <c r="S27" t="n">
-        <v>-8.196099999999999</v>
+        <v>-8.223000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-9.209300000000001</v>
+        <v>-9.224600000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>1.0131</v>
+        <v>1.0016</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.4745</v>
+        <v>-2.479600000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7173999999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>-3.2138</v>
+        <v>-3.197</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104690_W26.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104690_W26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>1.0032</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-0.8751999999999993</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104690_W26.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-3.197</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
